--- a/docs/SJ2025.xlsx
+++ b/docs/SJ2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edilbertosuarez/Documents/Proyectos/icfes/icfes-analyzer/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72EC5233-46BB-D344-9EED-E96D21F4BFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5C22A1-A284-5944-900C-9B791E45FF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" xr2:uid="{00CE87F9-71CC-9C44-B6DC-24EC0DACDD5E}"/>
+    <workbookView xWindow="4460" yWindow="500" windowWidth="21140" windowHeight="15500" xr2:uid="{00CE87F9-71CC-9C44-B6DC-24EC0DACDD5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="142">
   <si>
     <t>Grupo</t>
   </si>
@@ -74,15 +74,6 @@
     <t>Apellido</t>
   </si>
   <si>
-    <t>Percentil Lectura crítica</t>
-  </si>
-  <si>
-    <t>Percentil Matemáticas</t>
-  </si>
-  <si>
-    <t>Percentil Sociales</t>
-  </si>
-  <si>
     <t>ACEVEDO OCAMPO</t>
   </si>
   <si>
@@ -471,21 +462,6 @@
   </si>
   <si>
     <t>11°3</t>
-  </si>
-  <si>
-    <t>Percentil Naturales</t>
-  </si>
-  <si>
-    <t>Percentil Inglés</t>
-  </si>
-  <si>
-    <t>Competencia</t>
-  </si>
-  <si>
-    <t>Componente</t>
-  </si>
-  <si>
-    <t>% Acierto</t>
   </si>
 </sst>
 </file>
@@ -871,14 +847,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8049E5-A74E-1849-8EE1-5BE190AEA293}">
-  <dimension ref="A1:R83"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="11" max="11" width="17.1640625" customWidth="1"/>
     <col min="12" max="12" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -909,43 +885,19 @@
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P1" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>147</v>
-      </c>
-      <c r="R1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E2">
         <v>50</v>
@@ -966,18 +918,18 @@
         <v>233</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E3">
         <v>62</v>
@@ -998,18 +950,18 @@
         <v>287</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E4">
         <v>59</v>
@@ -1028,18 +980,18 @@
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E5">
         <v>43</v>
@@ -1058,18 +1010,18 @@
         <v>231</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E6">
         <v>43</v>
@@ -1088,18 +1040,18 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E7">
         <v>66</v>
@@ -1120,18 +1072,18 @@
         <v>295</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E8">
         <v>51</v>
@@ -1152,18 +1104,18 @@
         <v>244</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E9">
         <v>48</v>
@@ -1184,18 +1136,18 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E10">
         <v>48</v>
@@ -1216,18 +1168,18 @@
         <v>259</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E11">
         <v>24</v>
@@ -1246,18 +1198,18 @@
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E12">
         <v>58</v>
@@ -1276,18 +1228,18 @@
         <v>268</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E13">
         <v>61</v>
@@ -1308,18 +1260,18 @@
         <v>277</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E14">
         <v>52</v>
@@ -1338,18 +1290,18 @@
         <v>235</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E15">
         <v>61</v>
@@ -1370,18 +1322,18 @@
         <v>319</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E16">
         <v>58</v>
@@ -1407,13 +1359,13 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E17">
         <v>71</v>
@@ -1439,13 +1391,13 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E18">
         <v>69</v>
@@ -1471,13 +1423,13 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>68</v>
@@ -1503,13 +1455,13 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E20">
         <v>68</v>
@@ -1535,13 +1487,13 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E21">
         <v>55</v>
@@ -1567,13 +1519,13 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E22">
         <v>50</v>
@@ -1599,13 +1551,13 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>69</v>
@@ -1631,13 +1583,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E24">
         <v>64</v>
@@ -1663,13 +1615,13 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E25">
         <v>76</v>
@@ -1695,13 +1647,13 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E26">
         <v>62</v>
@@ -1727,13 +1679,13 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E27">
         <v>61</v>
@@ -1759,13 +1711,13 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E28">
         <v>59</v>
@@ -1791,13 +1743,13 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E29">
         <v>58</v>
@@ -1823,13 +1775,13 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E30">
         <v>56</v>
@@ -1855,13 +1807,13 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E31">
         <v>65</v>
@@ -1887,13 +1839,13 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E32">
         <v>66</v>
@@ -1919,13 +1871,13 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E33">
         <v>68</v>
@@ -1951,13 +1903,13 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E34">
         <v>64</v>
@@ -1983,13 +1935,13 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E35">
         <v>67</v>
@@ -2015,13 +1967,13 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C36" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D36" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E36">
         <v>51</v>
@@ -2047,13 +1999,13 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E37">
         <v>64</v>
@@ -2079,13 +2031,13 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E38">
         <v>66</v>
@@ -2111,13 +2063,13 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E39">
         <v>67</v>
@@ -2143,13 +2095,13 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E40">
         <v>63</v>
@@ -2175,13 +2127,13 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E41">
         <v>70</v>
@@ -2207,13 +2159,13 @@
         <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E42">
         <v>63</v>
@@ -2239,13 +2191,13 @@
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E43">
         <v>63</v>
@@ -2271,13 +2223,13 @@
         <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C44" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E44">
         <v>52</v>
@@ -2303,13 +2255,13 @@
         <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D45" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E45">
         <v>56</v>
@@ -2335,13 +2287,13 @@
         <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E46">
         <v>66</v>
@@ -2367,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C47" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E47">
         <v>60</v>
@@ -2399,13 +2351,13 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E48">
         <v>75</v>
@@ -2431,13 +2383,13 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E49">
         <v>64</v>
@@ -2463,13 +2415,13 @@
         <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D50" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E50">
         <v>71</v>
@@ -2495,13 +2447,13 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C51" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D51" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E51">
         <v>71</v>
@@ -2527,13 +2479,13 @@
         <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D52" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E52">
         <v>70</v>
@@ -2559,13 +2511,13 @@
         <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E53">
         <v>74</v>
@@ -2591,13 +2543,13 @@
         <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E54">
         <v>65</v>
@@ -2623,13 +2575,13 @@
         <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C55" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D55" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E55">
         <v>68</v>
@@ -2655,13 +2607,13 @@
         <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C56" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D56" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E56">
         <v>62</v>
@@ -2687,13 +2639,13 @@
         <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C57" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E57">
         <v>61</v>
@@ -2719,13 +2671,13 @@
         <v>10</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D58" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E58">
         <v>66</v>
@@ -2751,13 +2703,13 @@
         <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C59" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D59" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E59">
         <v>68</v>
@@ -2783,13 +2735,13 @@
         <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E60">
         <v>68</v>
@@ -2815,13 +2767,13 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C61" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D61" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E61">
         <v>66</v>
@@ -2847,13 +2799,13 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C62" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D62" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E62">
         <v>59</v>
@@ -2879,13 +2831,13 @@
         <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C63" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D63" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E63">
         <v>59</v>
@@ -2911,13 +2863,13 @@
         <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C64" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D64" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E64">
         <v>57</v>
@@ -2943,13 +2895,13 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D65" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E65">
         <v>70</v>
@@ -2975,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C66" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D66" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E66">
         <v>59</v>
@@ -3007,13 +2959,13 @@
         <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C67" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E67">
         <v>67</v>
@@ -3039,13 +2991,13 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D68" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E68">
         <v>65</v>
@@ -3071,13 +3023,13 @@
         <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D69" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E69">
         <v>100</v>
@@ -3103,13 +3055,13 @@
         <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C70" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D70" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E70">
         <v>79</v>
@@ -3135,13 +3087,13 @@
         <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C71" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D71" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E71">
         <v>54</v>
@@ -3167,13 +3119,13 @@
         <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C72" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E72">
         <v>69</v>
@@ -3199,13 +3151,13 @@
         <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C73" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D73" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E73">
         <v>50</v>
@@ -3231,13 +3183,13 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C74" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D74" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E74">
         <v>49</v>
@@ -3263,13 +3215,13 @@
         <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C75" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D75" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E75">
         <v>39</v>
@@ -3295,13 +3247,13 @@
         <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C76" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D76" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E76">
         <v>56</v>
@@ -3327,13 +3279,13 @@
         <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C77" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D77" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E77">
         <v>61</v>
@@ -3359,13 +3311,13 @@
         <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C78" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D78" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E78">
         <v>56</v>
@@ -3391,13 +3343,13 @@
         <v>10</v>
       </c>
       <c r="B79" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C79" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D79" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E79">
         <v>70</v>
@@ -3423,13 +3375,13 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C80" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D80" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E80">
         <v>61</v>
@@ -3455,13 +3407,13 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C81" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D81" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E81">
         <v>57</v>
@@ -3487,13 +3439,13 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C82" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D82" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E82">
         <v>63</v>
@@ -3519,13 +3471,13 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C83" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D83" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E83">
         <v>52</v>

--- a/docs/SJ2025.xlsx
+++ b/docs/SJ2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edilbertosuarez/Documents/Proyectos/icfes/icfes-analyzer/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184952FB-202F-804D-B8C7-DF2E9D18F3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE30549D-6002-A741-B0B0-13699A608ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" xr2:uid="{00CE87F9-71CC-9C44-B6DC-24EC0DACDD5E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00CE87F9-71CC-9C44-B6DC-24EC0DACDD5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -542,11 +542,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -923,34 +922,34 @@
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>134</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>143</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>144</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>145</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>146</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>138</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" t="s">
         <v>142</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" t="s">
         <v>141</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" t="s">
         <v>140</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" t="s">
         <v>139</v>
       </c>
     </row>
@@ -959,7 +958,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
         <v>108</v>
@@ -1083,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
         <v>94</v>
@@ -1137,7 +1136,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
         <v>94</v>
@@ -1199,7 +1198,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" t="s">
         <v>107</v>
@@ -1261,7 +1260,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
         <v>135</v>
@@ -1385,7 +1384,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
         <v>111</v>
@@ -1447,7 +1446,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
         <v>92</v>
@@ -1509,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s">
         <v>120</v>
@@ -1571,7 +1570,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
         <v>101</v>
@@ -1633,7 +1632,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
         <v>119</v>
@@ -1695,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
         <v>106</v>
@@ -1757,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C15" t="s">
         <v>115</v>
@@ -1819,7 +1818,7 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
         <v>124</v>
@@ -1943,7 +1942,7 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
         <v>102</v>
@@ -2005,7 +2004,7 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
         <v>102</v>
@@ -2129,7 +2128,7 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
         <v>93</v>
@@ -2253,7 +2252,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
         <v>93</v>
@@ -2315,7 +2314,7 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
         <v>93</v>
@@ -2377,7 +2376,7 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C25" t="s">
         <v>93</v>
@@ -2563,7 +2562,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
         <v>118</v>
@@ -2803,7 +2802,7 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C32" t="s">
         <v>98</v>
@@ -2865,7 +2864,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C33" t="s">
         <v>125</v>
@@ -2927,7 +2926,7 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
         <v>112</v>
@@ -3051,7 +3050,7 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
         <v>112</v>
@@ -3175,7 +3174,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
         <v>121</v>
@@ -3237,7 +3236,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
         <v>121</v>
@@ -3299,7 +3298,7 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
         <v>121</v>
@@ -3361,7 +3360,7 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
         <v>136</v>
@@ -3423,7 +3422,7 @@
         <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C42" t="s">
         <v>117</v>
@@ -3485,7 +3484,7 @@
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C43" t="s">
         <v>117</v>
@@ -3609,7 +3608,7 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C45" t="s">
         <v>91</v>
@@ -3663,7 +3662,7 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
         <v>89</v>
@@ -3841,7 +3840,7 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C49" t="s">
         <v>89</v>
@@ -3965,7 +3964,7 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C51" t="s">
         <v>129</v>
@@ -4089,7 +4088,7 @@
         <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C53" t="s">
         <v>104</v>
@@ -4151,7 +4150,7 @@
         <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
@@ -4213,7 +4212,7 @@
         <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" t="s">
         <v>88</v>
@@ -4275,7 +4274,7 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C56" t="s">
         <v>88</v>
@@ -4337,7 +4336,7 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C57" t="s">
         <v>88</v>
@@ -4399,7 +4398,7 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C58" t="s">
         <v>88</v>
@@ -4523,7 +4522,7 @@
         <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C60" t="s">
         <v>88</v>
@@ -4585,7 +4584,7 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C61" t="s">
         <v>88</v>
@@ -4647,7 +4646,7 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C62" t="s">
         <v>88</v>
@@ -4833,7 +4832,7 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C65" t="s">
         <v>99</v>
@@ -4895,7 +4894,7 @@
         <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C66" t="s">
         <v>105</v>
@@ -4957,7 +4956,7 @@
         <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C67" t="s">
         <v>105</v>
@@ -5081,7 +5080,7 @@
         <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C69" t="s">
         <v>114</v>
@@ -5143,7 +5142,7 @@
         <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C70" t="s">
         <v>100</v>
@@ -5267,7 +5266,7 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C72" t="s">
         <v>90</v>
@@ -5321,7 +5320,7 @@
         <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C73" t="s">
         <v>90</v>
@@ -5383,7 +5382,7 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C74" t="s">
         <v>90</v>
@@ -5445,7 +5444,7 @@
         <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C75" t="s">
         <v>90</v>
@@ -5507,7 +5506,7 @@
         <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C76" t="s">
         <v>130</v>
@@ -5569,7 +5568,7 @@
         <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C77" t="s">
         <v>123</v>
@@ -5755,7 +5754,7 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C80" t="s">
         <v>95</v>
@@ -5871,7 +5870,7 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C82" t="s">
         <v>109</v>
@@ -5991,6 +5990,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T83" xr:uid="{EB8049E5-A74E-1849-8EE1-5BE190AEA293}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
